--- a/南京江北新区政务AI办公助手功能清单.xlsx
+++ b/南京江北新区政务AI办公助手功能清单.xlsx
@@ -1,14 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\marketingforce\marketforce\南京项目\南京江北新区政务AI智能体平台20260724\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="21600" windowHeight="9555"/>
+    <workbookView windowWidth="21600" windowHeight="9555" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="功能清单" sheetId="1" r:id="rId1"/>
     <sheet name="角色权限摘要" sheetId="2" r:id="rId2"/>
+    <sheet name="菜单管理权限" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,9 +34,16 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="606" uniqueCount="326">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="729" uniqueCount="377">
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>南京江北新区政务</t>
     </r>
     <r>
@@ -167,6 +180,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>支持搜索并选择</t>
     </r>
     <r>
@@ -223,6 +242,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>一次最多上传</t>
     </r>
     <r>
@@ -282,6 +307,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>读取本轮已生成内容，支持</t>
     </r>
     <r>
@@ -410,6 +441,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>按文种选择对应结构，缺失事实以</t>
     </r>
     <r>
@@ -442,6 +479,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>用户只补充任一已知信息即可先生成，其余信息用</t>
     </r>
     <r>
@@ -591,6 +634,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
       <t>PPT</t>
     </r>
     <r>
@@ -605,6 +654,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>根据材料生成汇报结构和版式统一的</t>
     </r>
     <r>
@@ -628,6 +683,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">PPT </t>
     </r>
     <r>
@@ -735,6 +796,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>政务协同</t>
     </r>
     <r>
@@ -803,6 +870,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>展示任务名称、智能体、状态和当前节点，如</t>
     </r>
     <r>
@@ -841,6 +914,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">PPT </t>
     </r>
     <r>
@@ -1068,6 +1147,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">11 </t>
     </r>
     <r>
@@ -1142,6 +1227,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>维护</t>
     </r>
     <r>
@@ -1165,6 +1256,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
       <t>PPT</t>
     </r>
     <r>
@@ -1291,6 +1388,159 @@
   <si>
     <t>不默认查看个人知识正文；业务数据查询仍受数据主题和部门权限控制</t>
   </si>
+  <si>
+    <t>一级菜单</t>
+  </si>
+  <si>
+    <t>一级菜单按钮</t>
+  </si>
+  <si>
+    <t>二级菜单</t>
+  </si>
+  <si>
+    <t>二级菜单按钮</t>
+  </si>
+  <si>
+    <t>可使用角色</t>
+  </si>
+  <si>
+    <t>首页</t>
+  </si>
+  <si>
+    <t>智能体广场</t>
+  </si>
+  <si>
+    <t>选择模板</t>
+  </si>
+  <si>
+    <t>配置更多模板</t>
+  </si>
+  <si>
+    <t>使用连接器</t>
+  </si>
+  <si>
+    <t>上传文件</t>
+  </si>
+  <si>
+    <t>创建文件夹</t>
+  </si>
+  <si>
+    <t>修改文件夹名称</t>
+  </si>
+  <si>
+    <t>删除文件夹</t>
+  </si>
+  <si>
+    <t>查看文件</t>
+  </si>
+  <si>
+    <t>下载文件</t>
+  </si>
+  <si>
+    <t>删除文件</t>
+  </si>
+  <si>
+    <t>组织知识库</t>
+  </si>
+  <si>
+    <t>查看</t>
+  </si>
+  <si>
+    <t>下载</t>
+  </si>
+  <si>
+    <t>上传到个人知识库</t>
+  </si>
+  <si>
+    <t>开始使用</t>
+  </si>
+  <si>
+    <t>配置治理中心</t>
+  </si>
+  <si>
+    <t>智能体管理</t>
+  </si>
+  <si>
+    <t>配置部门</t>
+  </si>
+  <si>
+    <t>业务连接器管理</t>
+  </si>
+  <si>
+    <t>智能体模板管理</t>
+  </si>
+  <si>
+    <t>新增模板</t>
+  </si>
+  <si>
+    <t>修改记录</t>
+  </si>
+  <si>
+    <t>复制模板</t>
+  </si>
+  <si>
+    <t>发布到部门</t>
+  </si>
+  <si>
+    <t>发布到公共</t>
+  </si>
+  <si>
+    <t>撤回</t>
+  </si>
+  <si>
+    <t>恢复角色默认值</t>
+  </si>
+  <si>
+    <t>保存并应用</t>
+  </si>
+  <si>
+    <t>用户管理</t>
+  </si>
+  <si>
+    <t>委办局管理员(仅可看自己委办局用户)、系统管理员</t>
+  </si>
+  <si>
+    <t>启用/禁用</t>
+  </si>
+  <si>
+    <t>组织机构</t>
+  </si>
+  <si>
+    <t>角色管理</t>
+  </si>
+  <si>
+    <t>新建角色</t>
+  </si>
+  <si>
+    <t>使用菜单范围</t>
+  </si>
+  <si>
+    <t>菜单管理</t>
+  </si>
+  <si>
+    <t>修改菜单名称</t>
+  </si>
+  <si>
+    <t>修改按钮名称</t>
+  </si>
+  <si>
+    <t>新增菜单</t>
+  </si>
+  <si>
+    <t>新增按钮</t>
+  </si>
+  <si>
+    <t>删除菜单</t>
+  </si>
+  <si>
+    <t>删除按钮</t>
+  </si>
+  <si>
+    <t>操作日志</t>
+  </si>
+  <si>
+    <t>委办局管理员(仅可看自己委办局数据)、系统管理员</t>
+  </si>
 </sst>
 </file>
 
@@ -1302,10 +1552,21 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="32">
+  <fonts count="34">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1758,12 +2019,64 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="15">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1793,21 +2106,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFD7E4EA"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1911,31 +2209,22 @@
     </border>
   </borders>
   <cellStyleXfs count="50">
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1944,168 +2233,201 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="6" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="6" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="6" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="49" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2582,1956 +2904,1956 @@
   <dimension ref="A1:G85"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="16.3166666666667" style="9" customWidth="1"/>
-    <col min="2" max="2" width="29.375" style="9" customWidth="1"/>
-    <col min="3" max="3" width="10.5" style="9" customWidth="1"/>
-    <col min="4" max="4" width="37.8166666666667" style="9" customWidth="1"/>
-    <col min="5" max="5" width="14.125" style="9" customWidth="1"/>
-    <col min="6" max="6" width="51.3166666666667" style="9" customWidth="1"/>
-    <col min="7" max="7" width="27.25" style="9" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="9"/>
+    <col min="1" max="1" width="16.3166666666667" style="17" customWidth="1"/>
+    <col min="2" max="2" width="29.375" style="17" customWidth="1"/>
+    <col min="3" max="3" width="10.5" style="17" customWidth="1"/>
+    <col min="4" max="4" width="37.8166666666667" style="17" customWidth="1"/>
+    <col min="5" max="5" width="14.125" style="17" customWidth="1"/>
+    <col min="6" max="6" width="51.3166666666667" style="17" customWidth="1"/>
+    <col min="7" max="7" width="27.25" style="17" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="17"/>
   </cols>
   <sheetData>
-    <row r="1" s="9" customFormat="1" ht="23.25" spans="1:7">
-      <c r="A1" s="10" t="s">
+    <row r="1" s="17" customFormat="1" ht="23.25" spans="1:7">
+      <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-    </row>
-    <row r="2" s="9" customFormat="1" spans="1:7">
-      <c r="A2" s="12" t="s">
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+    </row>
+    <row r="2" s="17" customFormat="1" spans="1:7">
+      <c r="A2" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="E2" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="F2" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="G2" s="20" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="3" ht="25.5" spans="1:7">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="D3" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="14" t="s">
+      <c r="E3" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="14" t="s">
+      <c r="F3" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="15" t="s">
+      <c r="G3" s="23" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="4" ht="25.5" spans="1:7">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="14" t="s">
+      <c r="D4" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="14" t="s">
+      <c r="E4" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="F4" s="14" t="s">
+      <c r="F4" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="G4" s="15" t="s">
+      <c r="G4" s="23" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="5" ht="25.5" spans="1:7">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="D5" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="E5" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="F5" s="14" t="s">
+      <c r="F5" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="G5" s="15" t="s">
+      <c r="G5" s="23" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="6" ht="25.5" spans="1:7">
-      <c r="A6" s="13" t="s">
+      <c r="A6" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="14" t="s">
+      <c r="D6" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="14" t="s">
+      <c r="E6" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="F6" s="14" t="s">
+      <c r="F6" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="G6" s="15" t="s">
+      <c r="G6" s="23" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="7" ht="25.5" spans="1:7">
-      <c r="A7" s="13" t="s">
+      <c r="A7" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="14" t="s">
+      <c r="B7" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="14" t="s">
+      <c r="C7" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="14" t="s">
+      <c r="D7" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="E7" s="14" t="s">
+      <c r="E7" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="F7" s="14" t="s">
+      <c r="F7" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="G7" s="15" t="s">
+      <c r="G7" s="23" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="8" ht="38.25" spans="1:7">
-      <c r="A8" s="13" t="s">
+      <c r="A8" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="B8" s="14" t="s">
+      <c r="B8" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="C8" s="14" t="s">
+      <c r="C8" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="D8" s="14" t="s">
+      <c r="D8" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="E8" s="14" t="s">
+      <c r="E8" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="F8" s="14" t="s">
+      <c r="F8" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="G8" s="15" t="s">
+      <c r="G8" s="23" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="9" ht="38.25" spans="1:7">
-      <c r="A9" s="13" t="s">
+      <c r="A9" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="B9" s="14" t="s">
+      <c r="B9" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="14" t="s">
+      <c r="C9" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="D9" s="14" t="s">
+      <c r="D9" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="E9" s="14" t="s">
+      <c r="E9" s="22" t="s">
         <v>37</v>
       </c>
-      <c r="F9" s="14" t="s">
+      <c r="F9" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="G9" s="15" t="s">
+      <c r="G9" s="23" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="10" ht="38.25" spans="1:7">
-      <c r="A10" s="13" t="s">
+      <c r="A10" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="B10" s="14" t="s">
+      <c r="B10" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="C10" s="14" t="s">
+      <c r="C10" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="D10" s="14" t="s">
+      <c r="D10" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="E10" s="14" t="s">
+      <c r="E10" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="F10" s="14" t="s">
+      <c r="F10" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="G10" s="15" t="s">
+      <c r="G10" s="23" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="11" ht="38.25" spans="1:7">
-      <c r="A11" s="13" t="s">
+      <c r="A11" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="14" t="s">
+      <c r="B11" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="C11" s="14" t="s">
+      <c r="C11" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="D11" s="14" t="s">
+      <c r="D11" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="E11" s="14" t="s">
+      <c r="E11" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="F11" s="14" t="s">
+      <c r="F11" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="G11" s="15" t="s">
+      <c r="G11" s="23" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="12" ht="38.25" spans="1:7">
-      <c r="A12" s="13" t="s">
+      <c r="A12" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="B12" s="14" t="s">
+      <c r="B12" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="14" t="s">
+      <c r="C12" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="D12" s="14" t="s">
+      <c r="D12" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="E12" s="14" t="s">
+      <c r="E12" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="F12" s="14" t="s">
+      <c r="F12" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="G12" s="15" t="s">
+      <c r="G12" s="23" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="13" ht="38.25" spans="1:7">
-      <c r="A13" s="13" t="s">
+      <c r="A13" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="14" t="s">
+      <c r="B13" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="14" t="s">
+      <c r="C13" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="D13" s="14" t="s">
+      <c r="D13" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="E13" s="14" t="s">
+      <c r="E13" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="F13" s="14" t="s">
+      <c r="F13" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="G13" s="15" t="s">
+      <c r="G13" s="23" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="14" ht="38.25" spans="1:7">
-      <c r="A14" s="13" t="s">
+      <c r="A14" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="B14" s="14" t="s">
+      <c r="B14" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="C14" s="14" t="s">
+      <c r="C14" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="D14" s="14" t="s">
+      <c r="D14" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="E14" s="14" t="s">
+      <c r="E14" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="F14" s="14" t="s">
+      <c r="F14" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="G14" s="15" t="s">
+      <c r="G14" s="23" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="15" ht="38.25" spans="1:7">
-      <c r="A15" s="13" t="s">
+      <c r="A15" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="B15" s="14" t="s">
+      <c r="B15" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="C15" s="14" t="s">
+      <c r="C15" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="D15" s="14" t="s">
+      <c r="D15" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="E15" s="14" t="s">
+      <c r="E15" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="F15" s="14" t="s">
+      <c r="F15" s="22" t="s">
         <v>52</v>
       </c>
-      <c r="G15" s="15" t="s">
+      <c r="G15" s="23" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="16" ht="38.25" spans="1:7">
-      <c r="A16" s="13" t="s">
+      <c r="A16" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="B16" s="14" t="s">
+      <c r="B16" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="C16" s="14" t="s">
+      <c r="C16" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="D16" s="14" t="s">
+      <c r="D16" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="E16" s="14" t="s">
+      <c r="E16" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="F16" s="14" t="s">
+      <c r="F16" s="22" t="s">
         <v>57</v>
       </c>
-      <c r="G16" s="15" t="s">
+      <c r="G16" s="23" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="17" ht="38.25" spans="1:7">
-      <c r="A17" s="13" t="s">
+      <c r="A17" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="B17" s="14" t="s">
+      <c r="B17" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="C17" s="14" t="s">
+      <c r="C17" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="D17" s="14" t="s">
+      <c r="D17" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="E17" s="14" t="s">
+      <c r="E17" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="F17" s="14" t="s">
+      <c r="F17" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="G17" s="15" t="s">
+      <c r="G17" s="23" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="18" ht="38.25" spans="1:7">
-      <c r="A18" s="13" t="s">
+      <c r="A18" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="B18" s="14" t="s">
+      <c r="B18" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="C18" s="14" t="s">
+      <c r="C18" s="22" t="s">
         <v>60</v>
       </c>
-      <c r="D18" s="14" t="s">
+      <c r="D18" s="22" t="s">
         <v>61</v>
       </c>
-      <c r="E18" s="14" t="s">
+      <c r="E18" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="F18" s="14" t="s">
+      <c r="F18" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="G18" s="15" t="s">
+      <c r="G18" s="23" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="19" ht="38.25" spans="1:7">
-      <c r="A19" s="13" t="s">
+      <c r="A19" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="B19" s="14" t="s">
+      <c r="B19" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="C19" s="14" t="s">
+      <c r="C19" s="22" t="s">
         <v>60</v>
       </c>
-      <c r="D19" s="14" t="s">
+      <c r="D19" s="22" t="s">
         <v>61</v>
       </c>
-      <c r="E19" s="14" t="s">
+      <c r="E19" s="22" t="s">
         <v>64</v>
       </c>
-      <c r="F19" s="14" t="s">
+      <c r="F19" s="22" t="s">
         <v>65</v>
       </c>
-      <c r="G19" s="15" t="s">
+      <c r="G19" s="23" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="20" ht="25.5" spans="1:7">
-      <c r="A20" s="13" t="s">
+      <c r="A20" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="B20" s="14" t="s">
+      <c r="B20" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="C20" s="14" t="s">
+      <c r="C20" s="22" t="s">
         <v>68</v>
       </c>
-      <c r="D20" s="14" t="s">
+      <c r="D20" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="E20" s="14" t="s">
+      <c r="E20" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="F20" s="14" t="s">
+      <c r="F20" s="22" t="s">
         <v>71</v>
       </c>
-      <c r="G20" s="15" t="s">
+      <c r="G20" s="23" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="21" ht="25.5" spans="1:7">
-      <c r="A21" s="13" t="s">
+      <c r="A21" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="B21" s="14" t="s">
+      <c r="B21" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="C21" s="14" t="s">
+      <c r="C21" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="D21" s="14" t="s">
+      <c r="D21" s="22" t="s">
         <v>73</v>
       </c>
-      <c r="E21" s="14" t="s">
+      <c r="E21" s="22" t="s">
         <v>74</v>
       </c>
-      <c r="F21" s="14" t="s">
+      <c r="F21" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="G21" s="15" t="s">
+      <c r="G21" s="23" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="22" ht="25.5" spans="1:7">
-      <c r="A22" s="13" t="s">
+      <c r="A22" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="B22" s="14" t="s">
+      <c r="B22" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="C22" s="14" t="s">
+      <c r="C22" s="22" t="s">
         <v>76</v>
       </c>
-      <c r="D22" s="14" t="s">
+      <c r="D22" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="E22" s="14" t="s">
+      <c r="E22" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="F22" s="14" t="s">
+      <c r="F22" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="G22" s="15" t="s">
+      <c r="G22" s="23" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="23" ht="25.5" spans="1:7">
-      <c r="A23" s="13" t="s">
+      <c r="A23" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="B23" s="14" t="s">
+      <c r="B23" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="C23" s="14" t="s">
+      <c r="C23" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="D23" s="14" t="s">
+      <c r="D23" s="22" t="s">
         <v>81</v>
       </c>
-      <c r="E23" s="14" t="s">
+      <c r="E23" s="22" t="s">
         <v>82</v>
       </c>
-      <c r="F23" s="14" t="s">
+      <c r="F23" s="22" t="s">
         <v>83</v>
       </c>
-      <c r="G23" s="15" t="s">
+      <c r="G23" s="23" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="24" ht="25.5" spans="1:7">
-      <c r="A24" s="13" t="s">
+      <c r="A24" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="B24" s="14" t="s">
+      <c r="B24" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="C24" s="14" t="s">
+      <c r="C24" s="22" t="s">
         <v>84</v>
       </c>
-      <c r="D24" s="14" t="s">
+      <c r="D24" s="22" t="s">
         <v>85</v>
       </c>
-      <c r="E24" s="14" t="s">
+      <c r="E24" s="22" t="s">
         <v>86</v>
       </c>
-      <c r="F24" s="14" t="s">
+      <c r="F24" s="22" t="s">
         <v>87</v>
       </c>
-      <c r="G24" s="15" t="s">
+      <c r="G24" s="23" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="25" ht="25.5" spans="1:7">
-      <c r="A25" s="13" t="s">
+      <c r="A25" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="B25" s="14" t="s">
+      <c r="B25" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="C25" s="14" t="s">
+      <c r="C25" s="22" t="s">
         <v>88</v>
       </c>
-      <c r="D25" s="14" t="s">
+      <c r="D25" s="22" t="s">
         <v>89</v>
       </c>
-      <c r="E25" s="14" t="s">
+      <c r="E25" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="F25" s="14" t="s">
+      <c r="F25" s="22" t="s">
         <v>91</v>
       </c>
-      <c r="G25" s="15" t="s">
+      <c r="G25" s="23" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="26" ht="25.5" spans="1:7">
-      <c r="A26" s="13" t="s">
+      <c r="A26" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="B26" s="14" t="s">
+      <c r="B26" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="C26" s="14" t="s">
+      <c r="C26" s="22" t="s">
         <v>92</v>
       </c>
-      <c r="D26" s="14" t="s">
+      <c r="D26" s="22" t="s">
         <v>93</v>
       </c>
-      <c r="E26" s="14" t="s">
+      <c r="E26" s="22" t="s">
         <v>94</v>
       </c>
-      <c r="F26" s="14" t="s">
+      <c r="F26" s="22" t="s">
         <v>95</v>
       </c>
-      <c r="G26" s="15" t="s">
+      <c r="G26" s="23" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="27" ht="25.5" spans="1:7">
-      <c r="A27" s="13" t="s">
+      <c r="A27" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="B27" s="14" t="s">
+      <c r="B27" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="C27" s="14" t="s">
+      <c r="C27" s="22" t="s">
         <v>96</v>
       </c>
-      <c r="D27" s="14" t="s">
+      <c r="D27" s="22" t="s">
         <v>97</v>
       </c>
-      <c r="E27" s="14" t="s">
+      <c r="E27" s="22" t="s">
         <v>98</v>
       </c>
-      <c r="F27" s="14" t="s">
+      <c r="F27" s="22" t="s">
         <v>99</v>
       </c>
-      <c r="G27" s="15" t="s">
+      <c r="G27" s="23" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="28" ht="25.5" spans="1:7">
-      <c r="A28" s="13" t="s">
+      <c r="A28" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="B28" s="14" t="s">
+      <c r="B28" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="C28" s="14" t="s">
+      <c r="C28" s="22" t="s">
         <v>100</v>
       </c>
-      <c r="D28" s="14" t="s">
+      <c r="D28" s="22" t="s">
         <v>101</v>
       </c>
-      <c r="E28" s="14" t="s">
+      <c r="E28" s="22" t="s">
         <v>102</v>
       </c>
-      <c r="F28" s="14" t="s">
+      <c r="F28" s="22" t="s">
         <v>103</v>
       </c>
-      <c r="G28" s="15" t="s">
+      <c r="G28" s="23" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="29" ht="25.5" spans="1:7">
-      <c r="A29" s="13" t="s">
+      <c r="A29" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="B29" s="14" t="s">
+      <c r="B29" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="C29" s="14" t="s">
+      <c r="C29" s="22" t="s">
         <v>104</v>
       </c>
-      <c r="D29" s="14" t="s">
+      <c r="D29" s="22" t="s">
         <v>105</v>
       </c>
-      <c r="E29" s="14" t="s">
+      <c r="E29" s="22" t="s">
         <v>106</v>
       </c>
-      <c r="F29" s="14" t="s">
+      <c r="F29" s="22" t="s">
         <v>107</v>
       </c>
-      <c r="G29" s="15" t="s">
+      <c r="G29" s="23" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="30" ht="25.5" spans="1:7">
-      <c r="A30" s="13" t="s">
+      <c r="A30" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="B30" s="14" t="s">
+      <c r="B30" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="C30" s="14" t="s">
+      <c r="C30" s="22" t="s">
         <v>108</v>
       </c>
-      <c r="D30" s="14" t="s">
+      <c r="D30" s="22" t="s">
         <v>109</v>
       </c>
-      <c r="E30" s="14" t="s">
+      <c r="E30" s="22" t="s">
         <v>110</v>
       </c>
-      <c r="F30" s="14" t="s">
+      <c r="F30" s="22" t="s">
         <v>111</v>
       </c>
-      <c r="G30" s="15" t="s">
+      <c r="G30" s="23" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="31" ht="25.5" spans="1:7">
-      <c r="A31" s="13" t="s">
+      <c r="A31" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="B31" s="14" t="s">
+      <c r="B31" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="C31" s="14" t="s">
+      <c r="C31" s="22" t="s">
         <v>112</v>
       </c>
-      <c r="D31" s="14" t="s">
+      <c r="D31" s="22" t="s">
         <v>113</v>
       </c>
-      <c r="E31" s="14" t="s">
+      <c r="E31" s="22" t="s">
         <v>114</v>
       </c>
-      <c r="F31" s="14" t="s">
+      <c r="F31" s="22" t="s">
         <v>115</v>
       </c>
-      <c r="G31" s="15" t="s">
+      <c r="G31" s="23" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="32" ht="25.5" spans="1:7">
-      <c r="A32" s="13" t="s">
+      <c r="A32" s="21" t="s">
         <v>116</v>
       </c>
-      <c r="B32" s="14" t="s">
+      <c r="B32" s="22" t="s">
         <v>117</v>
       </c>
-      <c r="C32" s="14" t="s">
+      <c r="C32" s="22" t="s">
         <v>118</v>
       </c>
-      <c r="D32" s="14" t="s">
+      <c r="D32" s="22" t="s">
         <v>119</v>
       </c>
-      <c r="E32" s="14" t="s">
+      <c r="E32" s="22" t="s">
         <v>120</v>
       </c>
-      <c r="F32" s="14" t="s">
+      <c r="F32" s="22" t="s">
         <v>121</v>
       </c>
-      <c r="G32" s="15" t="s">
+      <c r="G32" s="23" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="33" ht="25.5" spans="1:7">
-      <c r="A33" s="13" t="s">
+      <c r="A33" s="21" t="s">
         <v>116</v>
       </c>
-      <c r="B33" s="14" t="s">
+      <c r="B33" s="22" t="s">
         <v>117</v>
       </c>
-      <c r="C33" s="14" t="s">
+      <c r="C33" s="22" t="s">
         <v>122</v>
       </c>
-      <c r="D33" s="14" t="s">
+      <c r="D33" s="22" t="s">
         <v>123</v>
       </c>
-      <c r="E33" s="14" t="s">
+      <c r="E33" s="22" t="s">
         <v>124</v>
       </c>
-      <c r="F33" s="14" t="s">
+      <c r="F33" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="G33" s="15" t="s">
+      <c r="G33" s="23" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="34" ht="25.5" spans="1:7">
-      <c r="A34" s="13" t="s">
+      <c r="A34" s="21" t="s">
         <v>116</v>
       </c>
-      <c r="B34" s="14" t="s">
+      <c r="B34" s="22" t="s">
         <v>117</v>
       </c>
-      <c r="C34" s="14" t="s">
+      <c r="C34" s="22" t="s">
         <v>126</v>
       </c>
-      <c r="D34" s="14" t="s">
+      <c r="D34" s="22" t="s">
         <v>127</v>
       </c>
-      <c r="E34" s="14" t="s">
+      <c r="E34" s="22" t="s">
         <v>128</v>
       </c>
-      <c r="F34" s="14" t="s">
+      <c r="F34" s="22" t="s">
         <v>129</v>
       </c>
-      <c r="G34" s="15" t="s">
+      <c r="G34" s="23" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="35" ht="25.5" spans="1:7">
-      <c r="A35" s="13" t="s">
+      <c r="A35" s="21" t="s">
         <v>116</v>
       </c>
-      <c r="B35" s="14" t="s">
+      <c r="B35" s="22" t="s">
         <v>117</v>
       </c>
-      <c r="C35" s="14" t="s">
+      <c r="C35" s="22" t="s">
         <v>130</v>
       </c>
-      <c r="D35" s="14" t="s">
+      <c r="D35" s="22" t="s">
         <v>131</v>
       </c>
-      <c r="E35" s="14" t="s">
+      <c r="E35" s="22" t="s">
         <v>132</v>
       </c>
-      <c r="F35" s="14" t="s">
+      <c r="F35" s="22" t="s">
         <v>133</v>
       </c>
-      <c r="G35" s="15" t="s">
+      <c r="G35" s="23" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="36" ht="25.5" spans="1:7">
-      <c r="A36" s="13" t="s">
+      <c r="A36" s="21" t="s">
         <v>116</v>
       </c>
-      <c r="B36" s="14" t="s">
+      <c r="B36" s="22" t="s">
         <v>117</v>
       </c>
-      <c r="C36" s="16" t="s">
+      <c r="C36" s="24" t="s">
         <v>134</v>
       </c>
-      <c r="D36" s="14" t="s">
+      <c r="D36" s="22" t="s">
         <v>135</v>
       </c>
-      <c r="E36" s="16" t="s">
+      <c r="E36" s="24" t="s">
         <v>136</v>
       </c>
-      <c r="F36" s="14" t="s">
+      <c r="F36" s="22" t="s">
         <v>137</v>
       </c>
-      <c r="G36" s="15" t="s">
+      <c r="G36" s="23" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="37" ht="25.5" spans="1:7">
-      <c r="A37" s="13" t="s">
+      <c r="A37" s="21" t="s">
         <v>138</v>
       </c>
-      <c r="B37" s="14" t="s">
+      <c r="B37" s="22" t="s">
         <v>139</v>
       </c>
-      <c r="C37" s="14" t="s">
+      <c r="C37" s="22" t="s">
         <v>140</v>
       </c>
-      <c r="D37" s="14" t="s">
+      <c r="D37" s="22" t="s">
         <v>141</v>
       </c>
-      <c r="E37" s="14" t="s">
+      <c r="E37" s="22" t="s">
         <v>142</v>
       </c>
-      <c r="F37" s="14" t="s">
+      <c r="F37" s="22" t="s">
         <v>143</v>
       </c>
-      <c r="G37" s="15" t="s">
+      <c r="G37" s="23" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="38" ht="25.5" spans="1:7">
-      <c r="A38" s="13" t="s">
+      <c r="A38" s="21" t="s">
         <v>138</v>
       </c>
-      <c r="B38" s="14" t="s">
+      <c r="B38" s="22" t="s">
         <v>139</v>
       </c>
-      <c r="C38" s="14" t="s">
+      <c r="C38" s="22" t="s">
         <v>140</v>
       </c>
-      <c r="D38" s="14" t="s">
+      <c r="D38" s="22" t="s">
         <v>141</v>
       </c>
-      <c r="E38" s="14" t="s">
+      <c r="E38" s="22" t="s">
         <v>144</v>
       </c>
-      <c r="F38" s="14" t="s">
+      <c r="F38" s="22" t="s">
         <v>145</v>
       </c>
-      <c r="G38" s="15" t="s">
+      <c r="G38" s="23" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="39" ht="25.5" spans="1:7">
-      <c r="A39" s="13" t="s">
+      <c r="A39" s="21" t="s">
         <v>138</v>
       </c>
-      <c r="B39" s="14" t="s">
+      <c r="B39" s="22" t="s">
         <v>139</v>
       </c>
-      <c r="C39" s="14" t="s">
+      <c r="C39" s="22" t="s">
         <v>146</v>
       </c>
-      <c r="D39" s="14" t="s">
+      <c r="D39" s="22" t="s">
         <v>147</v>
       </c>
-      <c r="E39" s="14" t="s">
+      <c r="E39" s="22" t="s">
         <v>148</v>
       </c>
-      <c r="F39" s="14" t="s">
+      <c r="F39" s="22" t="s">
         <v>149</v>
       </c>
-      <c r="G39" s="15" t="s">
+      <c r="G39" s="23" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="40" ht="25.5" spans="1:7">
-      <c r="A40" s="13" t="s">
+      <c r="A40" s="21" t="s">
         <v>138</v>
       </c>
-      <c r="B40" s="14" t="s">
+      <c r="B40" s="22" t="s">
         <v>139</v>
       </c>
-      <c r="C40" s="14" t="s">
+      <c r="C40" s="22" t="s">
         <v>146</v>
       </c>
-      <c r="D40" s="14" t="s">
+      <c r="D40" s="22" t="s">
         <v>147</v>
       </c>
-      <c r="E40" s="14" t="s">
+      <c r="E40" s="22" t="s">
         <v>150</v>
       </c>
-      <c r="F40" s="14" t="s">
+      <c r="F40" s="22" t="s">
         <v>151</v>
       </c>
-      <c r="G40" s="15" t="s">
+      <c r="G40" s="23" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="41" ht="25.5" spans="1:7">
-      <c r="A41" s="13" t="s">
+      <c r="A41" s="21" t="s">
         <v>138</v>
       </c>
-      <c r="B41" s="14" t="s">
+      <c r="B41" s="22" t="s">
         <v>139</v>
       </c>
-      <c r="C41" s="14" t="s">
+      <c r="C41" s="22" t="s">
         <v>146</v>
       </c>
-      <c r="D41" s="14" t="s">
+      <c r="D41" s="22" t="s">
         <v>147</v>
       </c>
-      <c r="E41" s="14" t="s">
+      <c r="E41" s="22" t="s">
         <v>152</v>
       </c>
-      <c r="F41" s="14" t="s">
+      <c r="F41" s="22" t="s">
         <v>153</v>
       </c>
-      <c r="G41" s="15" t="s">
+      <c r="G41" s="23" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="42" ht="25.5" spans="1:7">
-      <c r="A42" s="13" t="s">
+      <c r="A42" s="21" t="s">
         <v>138</v>
       </c>
-      <c r="B42" s="14" t="s">
+      <c r="B42" s="22" t="s">
         <v>139</v>
       </c>
-      <c r="C42" s="14" t="s">
+      <c r="C42" s="22" t="s">
         <v>154</v>
       </c>
-      <c r="D42" s="14" t="s">
+      <c r="D42" s="22" t="s">
         <v>155</v>
       </c>
-      <c r="E42" s="14" t="s">
+      <c r="E42" s="22" t="s">
         <v>156</v>
       </c>
-      <c r="F42" s="14" t="s">
+      <c r="F42" s="22" t="s">
         <v>157</v>
       </c>
-      <c r="G42" s="15" t="s">
+      <c r="G42" s="23" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="43" ht="25.5" spans="1:7">
-      <c r="A43" s="13" t="s">
+      <c r="A43" s="21" t="s">
         <v>158</v>
       </c>
-      <c r="B43" s="14" t="s">
+      <c r="B43" s="22" t="s">
         <v>159</v>
       </c>
-      <c r="C43" s="14" t="s">
+      <c r="C43" s="22" t="s">
         <v>160</v>
       </c>
-      <c r="D43" s="14" t="s">
+      <c r="D43" s="22" t="s">
         <v>161</v>
       </c>
-      <c r="E43" s="14" t="s">
+      <c r="E43" s="22" t="s">
         <v>162</v>
       </c>
-      <c r="F43" s="14" t="s">
+      <c r="F43" s="22" t="s">
         <v>163</v>
       </c>
-      <c r="G43" s="15" t="s">
+      <c r="G43" s="23" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="44" ht="25.5" spans="1:7">
-      <c r="A44" s="13" t="s">
+      <c r="A44" s="21" t="s">
         <v>158</v>
       </c>
-      <c r="B44" s="14" t="s">
+      <c r="B44" s="22" t="s">
         <v>159</v>
       </c>
-      <c r="C44" s="14" t="s">
+      <c r="C44" s="22" t="s">
         <v>164</v>
       </c>
-      <c r="D44" s="14" t="s">
+      <c r="D44" s="22" t="s">
         <v>165</v>
       </c>
-      <c r="E44" s="14" t="s">
+      <c r="E44" s="22" t="s">
         <v>166</v>
       </c>
-      <c r="F44" s="14" t="s">
+      <c r="F44" s="22" t="s">
         <v>167</v>
       </c>
-      <c r="G44" s="15" t="s">
+      <c r="G44" s="23" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="45" ht="25.5" spans="1:7">
-      <c r="A45" s="13" t="s">
+      <c r="A45" s="21" t="s">
         <v>158</v>
       </c>
-      <c r="B45" s="14" t="s">
+      <c r="B45" s="22" t="s">
         <v>159</v>
       </c>
-      <c r="C45" s="14" t="s">
+      <c r="C45" s="22" t="s">
         <v>164</v>
       </c>
-      <c r="D45" s="14" t="s">
+      <c r="D45" s="22" t="s">
         <v>165</v>
       </c>
-      <c r="E45" s="14" t="s">
+      <c r="E45" s="22" t="s">
         <v>168</v>
       </c>
-      <c r="F45" s="14" t="s">
+      <c r="F45" s="22" t="s">
         <v>169</v>
       </c>
-      <c r="G45" s="15" t="s">
+      <c r="G45" s="23" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="46" ht="25.5" spans="1:7">
-      <c r="A46" s="13" t="s">
+      <c r="A46" s="21" t="s">
         <v>158</v>
       </c>
-      <c r="B46" s="14" t="s">
+      <c r="B46" s="22" t="s">
         <v>159</v>
       </c>
-      <c r="C46" s="14" t="s">
+      <c r="C46" s="22" t="s">
         <v>164</v>
       </c>
-      <c r="D46" s="14" t="s">
+      <c r="D46" s="22" t="s">
         <v>165</v>
       </c>
-      <c r="E46" s="14" t="s">
+      <c r="E46" s="22" t="s">
         <v>170</v>
       </c>
-      <c r="F46" s="14" t="s">
+      <c r="F46" s="22" t="s">
         <v>171</v>
       </c>
-      <c r="G46" s="15" t="s">
+      <c r="G46" s="23" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="47" ht="25.5" spans="1:7">
-      <c r="A47" s="13" t="s">
+      <c r="A47" s="21" t="s">
         <v>158</v>
       </c>
-      <c r="B47" s="14" t="s">
+      <c r="B47" s="22" t="s">
         <v>159</v>
       </c>
-      <c r="C47" s="14" t="s">
+      <c r="C47" s="22" t="s">
         <v>164</v>
       </c>
-      <c r="D47" s="14" t="s">
+      <c r="D47" s="22" t="s">
         <v>165</v>
       </c>
-      <c r="E47" s="14" t="s">
+      <c r="E47" s="22" t="s">
         <v>172</v>
       </c>
-      <c r="F47" s="14" t="s">
+      <c r="F47" s="22" t="s">
         <v>173</v>
       </c>
-      <c r="G47" s="15" t="s">
+      <c r="G47" s="23" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="48" ht="25.5" spans="1:7">
-      <c r="A48" s="13" t="s">
+      <c r="A48" s="21" t="s">
         <v>158</v>
       </c>
-      <c r="B48" s="14" t="s">
+      <c r="B48" s="22" t="s">
         <v>159</v>
       </c>
-      <c r="C48" s="14" t="s">
+      <c r="C48" s="22" t="s">
         <v>164</v>
       </c>
-      <c r="D48" s="14" t="s">
+      <c r="D48" s="22" t="s">
         <v>165</v>
       </c>
-      <c r="E48" s="14" t="s">
+      <c r="E48" s="22" t="s">
         <v>174</v>
       </c>
-      <c r="F48" s="14" t="s">
+      <c r="F48" s="22" t="s">
         <v>175</v>
       </c>
-      <c r="G48" s="15" t="s">
+      <c r="G48" s="23" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="49" ht="25.5" spans="1:7">
-      <c r="A49" s="13" t="s">
+      <c r="A49" s="21" t="s">
         <v>158</v>
       </c>
-      <c r="B49" s="14" t="s">
+      <c r="B49" s="22" t="s">
         <v>159</v>
       </c>
-      <c r="C49" s="14" t="s">
+      <c r="C49" s="22" t="s">
         <v>164</v>
       </c>
-      <c r="D49" s="14" t="s">
+      <c r="D49" s="22" t="s">
         <v>165</v>
       </c>
-      <c r="E49" s="14" t="s">
+      <c r="E49" s="22" t="s">
         <v>176</v>
       </c>
-      <c r="F49" s="14" t="s">
+      <c r="F49" s="22" t="s">
         <v>177</v>
       </c>
-      <c r="G49" s="15" t="s">
+      <c r="G49" s="23" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="50" ht="25.5" spans="1:7">
-      <c r="A50" s="13" t="s">
+      <c r="A50" s="21" t="s">
         <v>158</v>
       </c>
-      <c r="B50" s="14" t="s">
+      <c r="B50" s="22" t="s">
         <v>159</v>
       </c>
-      <c r="C50" s="14" t="s">
+      <c r="C50" s="22" t="s">
         <v>178</v>
       </c>
-      <c r="D50" s="14" t="s">
+      <c r="D50" s="22" t="s">
         <v>179</v>
       </c>
-      <c r="E50" s="14" t="s">
+      <c r="E50" s="22" t="s">
         <v>180</v>
       </c>
-      <c r="F50" s="14" t="s">
+      <c r="F50" s="22" t="s">
         <v>181</v>
       </c>
-      <c r="G50" s="15" t="s">
+      <c r="G50" s="23" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="51" ht="25.5" spans="1:7">
-      <c r="A51" s="13" t="s">
+      <c r="A51" s="21" t="s">
         <v>182</v>
       </c>
-      <c r="B51" s="14" t="s">
+      <c r="B51" s="22" t="s">
         <v>183</v>
       </c>
-      <c r="C51" s="14" t="s">
+      <c r="C51" s="22" t="s">
         <v>184</v>
       </c>
-      <c r="D51" s="14" t="s">
+      <c r="D51" s="22" t="s">
         <v>185</v>
       </c>
-      <c r="E51" s="14" t="s">
+      <c r="E51" s="22" t="s">
         <v>186</v>
       </c>
-      <c r="F51" s="14" t="s">
+      <c r="F51" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="G51" s="15" t="s">
+      <c r="G51" s="23" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="52" ht="25.5" spans="1:7">
-      <c r="A52" s="13" t="s">
+      <c r="A52" s="21" t="s">
         <v>182</v>
       </c>
-      <c r="B52" s="14" t="s">
+      <c r="B52" s="22" t="s">
         <v>183</v>
       </c>
-      <c r="C52" s="14" t="s">
+      <c r="C52" s="22" t="s">
         <v>184</v>
       </c>
-      <c r="D52" s="14" t="s">
+      <c r="D52" s="22" t="s">
         <v>185</v>
       </c>
-      <c r="E52" s="14" t="s">
+      <c r="E52" s="22" t="s">
         <v>188</v>
       </c>
-      <c r="F52" s="14" t="s">
+      <c r="F52" s="22" t="s">
         <v>189</v>
       </c>
-      <c r="G52" s="15" t="s">
+      <c r="G52" s="23" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="53" ht="25.5" spans="1:7">
-      <c r="A53" s="13" t="s">
+      <c r="A53" s="21" t="s">
         <v>182</v>
       </c>
-      <c r="B53" s="14" t="s">
+      <c r="B53" s="22" t="s">
         <v>183</v>
       </c>
-      <c r="C53" s="14" t="s">
+      <c r="C53" s="22" t="s">
         <v>190</v>
       </c>
-      <c r="D53" s="14" t="s">
+      <c r="D53" s="22" t="s">
         <v>191</v>
       </c>
-      <c r="E53" s="14" t="s">
+      <c r="E53" s="22" t="s">
         <v>192</v>
       </c>
-      <c r="F53" s="16" t="s">
+      <c r="F53" s="24" t="s">
         <v>193</v>
       </c>
-      <c r="G53" s="15" t="s">
+      <c r="G53" s="23" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="54" ht="25.5" spans="1:7">
-      <c r="A54" s="13" t="s">
+      <c r="A54" s="21" t="s">
         <v>182</v>
       </c>
-      <c r="B54" s="14" t="s">
+      <c r="B54" s="22" t="s">
         <v>183</v>
       </c>
-      <c r="C54" s="14" t="s">
+      <c r="C54" s="22" t="s">
         <v>194</v>
       </c>
-      <c r="D54" s="14" t="s">
+      <c r="D54" s="22" t="s">
         <v>195</v>
       </c>
-      <c r="E54" s="14" t="s">
+      <c r="E54" s="22" t="s">
         <v>196</v>
       </c>
-      <c r="F54" s="14" t="s">
+      <c r="F54" s="22" t="s">
         <v>197</v>
       </c>
-      <c r="G54" s="15" t="s">
+      <c r="G54" s="23" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="55" ht="25.5" spans="1:7">
-      <c r="A55" s="13" t="s">
+      <c r="A55" s="21" t="s">
         <v>198</v>
       </c>
-      <c r="B55" s="14" t="s">
+      <c r="B55" s="22" t="s">
         <v>199</v>
       </c>
-      <c r="C55" s="14" t="s">
+      <c r="C55" s="22" t="s">
         <v>156</v>
       </c>
-      <c r="D55" s="14" t="s">
+      <c r="D55" s="22" t="s">
         <v>200</v>
       </c>
-      <c r="E55" s="14" t="s">
+      <c r="E55" s="22" t="s">
         <v>201</v>
       </c>
-      <c r="F55" s="14" t="s">
+      <c r="F55" s="22" t="s">
         <v>202</v>
       </c>
-      <c r="G55" s="15" t="s">
+      <c r="G55" s="23" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="56" ht="25.5" spans="1:7">
-      <c r="A56" s="13" t="s">
+      <c r="A56" s="21" t="s">
         <v>198</v>
       </c>
-      <c r="B56" s="14" t="s">
+      <c r="B56" s="22" t="s">
         <v>199</v>
       </c>
-      <c r="C56" s="14" t="s">
+      <c r="C56" s="22" t="s">
         <v>203</v>
       </c>
-      <c r="D56" s="14" t="s">
+      <c r="D56" s="22" t="s">
         <v>204</v>
       </c>
-      <c r="E56" s="14" t="s">
+      <c r="E56" s="22" t="s">
         <v>205</v>
       </c>
-      <c r="F56" s="14" t="s">
+      <c r="F56" s="22" t="s">
         <v>206</v>
       </c>
-      <c r="G56" s="15" t="s">
+      <c r="G56" s="23" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="57" ht="25.5" spans="1:7">
-      <c r="A57" s="13" t="s">
+      <c r="A57" s="21" t="s">
         <v>198</v>
       </c>
-      <c r="B57" s="14" t="s">
+      <c r="B57" s="22" t="s">
         <v>199</v>
       </c>
-      <c r="C57" s="14" t="s">
+      <c r="C57" s="22" t="s">
         <v>203</v>
       </c>
-      <c r="D57" s="14" t="s">
+      <c r="D57" s="22" t="s">
         <v>204</v>
       </c>
-      <c r="E57" s="14" t="s">
+      <c r="E57" s="22" t="s">
         <v>207</v>
       </c>
-      <c r="F57" s="14" t="s">
+      <c r="F57" s="22" t="s">
         <v>208</v>
       </c>
-      <c r="G57" s="15" t="s">
+      <c r="G57" s="23" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="58" ht="25.5" spans="1:7">
-      <c r="A58" s="13" t="s">
+      <c r="A58" s="21" t="s">
         <v>198</v>
       </c>
-      <c r="B58" s="14" t="s">
+      <c r="B58" s="22" t="s">
         <v>199</v>
       </c>
-      <c r="C58" s="14" t="s">
+      <c r="C58" s="22" t="s">
         <v>209</v>
       </c>
-      <c r="D58" s="14" t="s">
+      <c r="D58" s="22" t="s">
         <v>210</v>
       </c>
-      <c r="E58" s="14" t="s">
+      <c r="E58" s="22" t="s">
         <v>211</v>
       </c>
-      <c r="F58" s="14" t="s">
+      <c r="F58" s="22" t="s">
         <v>212</v>
       </c>
-      <c r="G58" s="15" t="s">
+      <c r="G58" s="23" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="59" ht="25.5" spans="1:7">
-      <c r="A59" s="13" t="s">
+      <c r="A59" s="21" t="s">
         <v>198</v>
       </c>
-      <c r="B59" s="14" t="s">
+      <c r="B59" s="22" t="s">
         <v>199</v>
       </c>
-      <c r="C59" s="14" t="s">
+      <c r="C59" s="22" t="s">
         <v>209</v>
       </c>
-      <c r="D59" s="14" t="s">
+      <c r="D59" s="22" t="s">
         <v>210</v>
       </c>
-      <c r="E59" s="14" t="s">
+      <c r="E59" s="22" t="s">
         <v>213</v>
       </c>
-      <c r="F59" s="14" t="s">
+      <c r="F59" s="22" t="s">
         <v>214</v>
       </c>
-      <c r="G59" s="15" t="s">
+      <c r="G59" s="23" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="60" ht="25.5" spans="1:7">
-      <c r="A60" s="13" t="s">
+      <c r="A60" s="21" t="s">
         <v>198</v>
       </c>
-      <c r="B60" s="14" t="s">
+      <c r="B60" s="22" t="s">
         <v>199</v>
       </c>
-      <c r="C60" s="14" t="s">
+      <c r="C60" s="22" t="s">
         <v>209</v>
       </c>
-      <c r="D60" s="14" t="s">
+      <c r="D60" s="22" t="s">
         <v>210</v>
       </c>
-      <c r="E60" s="14" t="s">
+      <c r="E60" s="22" t="s">
         <v>216</v>
       </c>
-      <c r="F60" s="14" t="s">
+      <c r="F60" s="22" t="s">
         <v>217</v>
       </c>
-      <c r="G60" s="15" t="s">
+      <c r="G60" s="23" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="61" ht="25.5" spans="1:7">
-      <c r="A61" s="13" t="s">
+      <c r="A61" s="21" t="s">
         <v>198</v>
       </c>
-      <c r="B61" s="14" t="s">
+      <c r="B61" s="22" t="s">
         <v>199</v>
       </c>
-      <c r="C61" s="14" t="s">
+      <c r="C61" s="22" t="s">
         <v>219</v>
       </c>
-      <c r="D61" s="14" t="s">
+      <c r="D61" s="22" t="s">
         <v>220</v>
       </c>
-      <c r="E61" s="14" t="s">
+      <c r="E61" s="22" t="s">
         <v>221</v>
       </c>
-      <c r="F61" s="14" t="s">
+      <c r="F61" s="22" t="s">
         <v>222</v>
       </c>
-      <c r="G61" s="15" t="s">
+      <c r="G61" s="23" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="62" ht="25.5" spans="1:7">
-      <c r="A62" s="13" t="s">
+      <c r="A62" s="21" t="s">
         <v>198</v>
       </c>
-      <c r="B62" s="14" t="s">
+      <c r="B62" s="22" t="s">
         <v>199</v>
       </c>
-      <c r="C62" s="14" t="s">
+      <c r="C62" s="22" t="s">
         <v>223</v>
       </c>
-      <c r="D62" s="14" t="s">
+      <c r="D62" s="22" t="s">
         <v>224</v>
       </c>
-      <c r="E62" s="14" t="s">
+      <c r="E62" s="22" t="s">
         <v>225</v>
       </c>
-      <c r="F62" s="14" t="s">
+      <c r="F62" s="22" t="s">
         <v>226</v>
       </c>
-      <c r="G62" s="15" t="s">
+      <c r="G62" s="23" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="63" ht="25.5" spans="1:7">
-      <c r="A63" s="13" t="s">
+      <c r="A63" s="21" t="s">
         <v>227</v>
       </c>
-      <c r="B63" s="14" t="s">
+      <c r="B63" s="22" t="s">
         <v>228</v>
       </c>
-      <c r="C63" s="14" t="s">
+      <c r="C63" s="22" t="s">
         <v>229</v>
       </c>
-      <c r="D63" s="14" t="s">
+      <c r="D63" s="22" t="s">
         <v>230</v>
       </c>
-      <c r="E63" s="14" t="s">
+      <c r="E63" s="22" t="s">
         <v>231</v>
       </c>
-      <c r="F63" s="14" t="s">
+      <c r="F63" s="22" t="s">
         <v>232</v>
       </c>
-      <c r="G63" s="15" t="s">
+      <c r="G63" s="23" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="64" ht="22.5" spans="1:7">
-      <c r="A64" s="13" t="s">
+      <c r="A64" s="21" t="s">
         <v>227</v>
       </c>
-      <c r="B64" s="14" t="s">
+      <c r="B64" s="22" t="s">
         <v>228</v>
       </c>
-      <c r="C64" s="14" t="s">
+      <c r="C64" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="D64" s="14" t="s">
+      <c r="D64" s="22" t="s">
         <v>233</v>
       </c>
-      <c r="E64" s="14" t="s">
+      <c r="E64" s="22" t="s">
         <v>234</v>
       </c>
-      <c r="F64" s="14" t="s">
+      <c r="F64" s="22" t="s">
         <v>235</v>
       </c>
-      <c r="G64" s="15" t="s">
+      <c r="G64" s="23" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="65" ht="22.5" spans="1:7">
-      <c r="A65" s="13" t="s">
+      <c r="A65" s="21" t="s">
         <v>227</v>
       </c>
-      <c r="B65" s="14" t="s">
+      <c r="B65" s="22" t="s">
         <v>228</v>
       </c>
-      <c r="C65" s="14" t="s">
+      <c r="C65" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="D65" s="14" t="s">
+      <c r="D65" s="22" t="s">
         <v>233</v>
       </c>
-      <c r="E65" s="14" t="s">
+      <c r="E65" s="22" t="s">
         <v>236</v>
       </c>
-      <c r="F65" s="14" t="s">
+      <c r="F65" s="22" t="s">
         <v>237</v>
       </c>
-      <c r="G65" s="15" t="s">
+      <c r="G65" s="23" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="66" ht="22.5" spans="1:7">
-      <c r="A66" s="13" t="s">
+      <c r="A66" s="21" t="s">
         <v>227</v>
       </c>
-      <c r="B66" s="14" t="s">
+      <c r="B66" s="22" t="s">
         <v>228</v>
       </c>
-      <c r="C66" s="14" t="s">
+      <c r="C66" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="D66" s="14" t="s">
+      <c r="D66" s="22" t="s">
         <v>233</v>
       </c>
-      <c r="E66" s="14" t="s">
+      <c r="E66" s="22" t="s">
         <v>238</v>
       </c>
-      <c r="F66" s="14" t="s">
+      <c r="F66" s="22" t="s">
         <v>239</v>
       </c>
-      <c r="G66" s="15" t="s">
+      <c r="G66" s="23" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="67" ht="22.5" spans="1:7">
-      <c r="A67" s="13" t="s">
+      <c r="A67" s="21" t="s">
         <v>227</v>
       </c>
-      <c r="B67" s="14" t="s">
+      <c r="B67" s="22" t="s">
         <v>228</v>
       </c>
-      <c r="C67" s="14" t="s">
+      <c r="C67" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="D67" s="14" t="s">
+      <c r="D67" s="22" t="s">
         <v>233</v>
       </c>
-      <c r="E67" s="14" t="s">
+      <c r="E67" s="22" t="s">
         <v>240</v>
       </c>
-      <c r="F67" s="14" t="s">
+      <c r="F67" s="22" t="s">
         <v>241</v>
       </c>
-      <c r="G67" s="15" t="s">
+      <c r="G67" s="23" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="68" spans="1:7">
-      <c r="A68" s="13" t="s">
+      <c r="A68" s="21" t="s">
         <v>242</v>
       </c>
-      <c r="B68" s="14" t="s">
+      <c r="B68" s="22" t="s">
         <v>243</v>
       </c>
-      <c r="C68" s="14" t="s">
+      <c r="C68" s="22" t="s">
         <v>244</v>
       </c>
-      <c r="D68" s="14" t="s">
+      <c r="D68" s="22" t="s">
         <v>245</v>
       </c>
-      <c r="E68" s="14" t="s">
+      <c r="E68" s="22" t="s">
         <v>246</v>
       </c>
-      <c r="F68" s="14" t="s">
+      <c r="F68" s="22" t="s">
         <v>247</v>
       </c>
-      <c r="G68" s="15" t="s">
+      <c r="G68" s="23" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="69" spans="1:7">
-      <c r="A69" s="13" t="s">
+      <c r="A69" s="21" t="s">
         <v>242</v>
       </c>
-      <c r="B69" s="14" t="s">
+      <c r="B69" s="22" t="s">
         <v>243</v>
       </c>
-      <c r="C69" s="14" t="s">
+      <c r="C69" s="22" t="s">
         <v>248</v>
       </c>
-      <c r="D69" s="14" t="s">
+      <c r="D69" s="22" t="s">
         <v>249</v>
       </c>
-      <c r="E69" s="14" t="s">
+      <c r="E69" s="22" t="s">
         <v>250</v>
       </c>
-      <c r="F69" s="14" t="s">
+      <c r="F69" s="22" t="s">
         <v>251</v>
       </c>
-      <c r="G69" s="15" t="s">
+      <c r="G69" s="23" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="70" spans="1:7">
-      <c r="A70" s="13" t="s">
+      <c r="A70" s="21" t="s">
         <v>242</v>
       </c>
-      <c r="B70" s="14" t="s">
+      <c r="B70" s="22" t="s">
         <v>243</v>
       </c>
-      <c r="C70" s="14" t="s">
+      <c r="C70" s="22" t="s">
         <v>252</v>
       </c>
-      <c r="D70" s="14" t="s">
+      <c r="D70" s="22" t="s">
         <v>253</v>
       </c>
-      <c r="E70" s="14" t="s">
+      <c r="E70" s="22" t="s">
         <v>254</v>
       </c>
-      <c r="F70" s="14" t="s">
+      <c r="F70" s="22" t="s">
         <v>255</v>
       </c>
-      <c r="G70" s="15" t="s">
+      <c r="G70" s="23" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="71" ht="25.5" spans="1:7">
-      <c r="A71" s="13" t="s">
+      <c r="A71" s="21" t="s">
         <v>256</v>
       </c>
-      <c r="B71" s="14" t="s">
+      <c r="B71" s="22" t="s">
         <v>257</v>
       </c>
-      <c r="C71" s="14" t="s">
+      <c r="C71" s="22" t="s">
         <v>258</v>
       </c>
-      <c r="D71" s="14" t="s">
+      <c r="D71" s="22" t="s">
         <v>259</v>
       </c>
-      <c r="E71" s="14" t="s">
+      <c r="E71" s="22" t="s">
         <v>260</v>
       </c>
-      <c r="F71" s="14" t="s">
+      <c r="F71" s="22" t="s">
         <v>261</v>
       </c>
-      <c r="G71" s="15" t="s">
+      <c r="G71" s="23" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="72" ht="25.5" spans="1:7">
-      <c r="A72" s="13" t="s">
+      <c r="A72" s="21" t="s">
         <v>256</v>
       </c>
-      <c r="B72" s="14" t="s">
+      <c r="B72" s="22" t="s">
         <v>257</v>
       </c>
-      <c r="C72" s="14" t="s">
+      <c r="C72" s="22" t="s">
         <v>258</v>
       </c>
-      <c r="D72" s="14" t="s">
+      <c r="D72" s="22" t="s">
         <v>259</v>
       </c>
-      <c r="E72" s="14" t="s">
+      <c r="E72" s="22" t="s">
         <v>262</v>
       </c>
-      <c r="F72" s="14" t="s">
+      <c r="F72" s="22" t="s">
         <v>263</v>
       </c>
-      <c r="G72" s="15" t="s">
+      <c r="G72" s="23" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="73" ht="25.5" spans="1:7">
-      <c r="A73" s="13" t="s">
+      <c r="A73" s="21" t="s">
         <v>256</v>
       </c>
-      <c r="B73" s="14" t="s">
+      <c r="B73" s="22" t="s">
         <v>257</v>
       </c>
-      <c r="C73" s="14" t="s">
+      <c r="C73" s="22" t="s">
         <v>264</v>
       </c>
-      <c r="D73" s="16" t="s">
+      <c r="D73" s="24" t="s">
         <v>265</v>
       </c>
-      <c r="E73" s="14" t="s">
+      <c r="E73" s="22" t="s">
         <v>266</v>
       </c>
-      <c r="F73" s="14" t="s">
+      <c r="F73" s="22" t="s">
         <v>267</v>
       </c>
-      <c r="G73" s="15" t="s">
+      <c r="G73" s="23" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="74" ht="25.5" spans="1:7">
-      <c r="A74" s="13" t="s">
+      <c r="A74" s="21" t="s">
         <v>256</v>
       </c>
-      <c r="B74" s="14" t="s">
+      <c r="B74" s="22" t="s">
         <v>257</v>
       </c>
-      <c r="C74" s="14" t="s">
+      <c r="C74" s="22" t="s">
         <v>68</v>
       </c>
-      <c r="D74" s="14" t="s">
+      <c r="D74" s="22" t="s">
         <v>268</v>
       </c>
-      <c r="E74" s="14" t="s">
+      <c r="E74" s="22" t="s">
         <v>269</v>
       </c>
-      <c r="F74" s="14" t="s">
+      <c r="F74" s="22" t="s">
         <v>270</v>
       </c>
-      <c r="G74" s="15" t="s">
+      <c r="G74" s="23" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="75" ht="25.5" spans="1:7">
-      <c r="A75" s="13" t="s">
+      <c r="A75" s="21" t="s">
         <v>256</v>
       </c>
-      <c r="B75" s="14" t="s">
+      <c r="B75" s="22" t="s">
         <v>257</v>
       </c>
-      <c r="C75" s="14" t="s">
+      <c r="C75" s="22" t="s">
         <v>118</v>
       </c>
-      <c r="D75" s="14" t="s">
+      <c r="D75" s="22" t="s">
         <v>271</v>
       </c>
-      <c r="E75" s="14" t="s">
+      <c r="E75" s="22" t="s">
         <v>272</v>
       </c>
-      <c r="F75" s="14" t="s">
+      <c r="F75" s="22" t="s">
         <v>273</v>
       </c>
-      <c r="G75" s="15" t="s">
+      <c r="G75" s="23" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="76" ht="25.5" spans="1:7">
-      <c r="A76" s="13" t="s">
+      <c r="A76" s="21" t="s">
         <v>256</v>
       </c>
-      <c r="B76" s="14" t="s">
+      <c r="B76" s="22" t="s">
         <v>257</v>
       </c>
-      <c r="C76" s="14" t="s">
+      <c r="C76" s="22" t="s">
         <v>122</v>
       </c>
-      <c r="D76" s="14" t="s">
+      <c r="D76" s="22" t="s">
         <v>274</v>
       </c>
-      <c r="E76" s="14" t="s">
+      <c r="E76" s="22" t="s">
         <v>275</v>
       </c>
-      <c r="F76" s="14" t="s">
+      <c r="F76" s="22" t="s">
         <v>276</v>
       </c>
-      <c r="G76" s="15" t="s">
+      <c r="G76" s="23" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="77" ht="25.5" spans="1:7">
-      <c r="A77" s="13" t="s">
+      <c r="A77" s="21" t="s">
         <v>256</v>
       </c>
-      <c r="B77" s="14" t="s">
+      <c r="B77" s="22" t="s">
         <v>257</v>
       </c>
-      <c r="C77" s="14" t="s">
+      <c r="C77" s="22" t="s">
         <v>112</v>
       </c>
-      <c r="D77" s="14" t="s">
+      <c r="D77" s="22" t="s">
         <v>277</v>
       </c>
-      <c r="E77" s="14" t="s">
+      <c r="E77" s="22" t="s">
         <v>278</v>
       </c>
-      <c r="F77" s="14" t="s">
+      <c r="F77" s="22" t="s">
         <v>279</v>
       </c>
-      <c r="G77" s="15" t="s">
+      <c r="G77" s="23" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="78" ht="25.5" spans="1:7">
-      <c r="A78" s="13" t="s">
+      <c r="A78" s="21" t="s">
         <v>256</v>
       </c>
-      <c r="B78" s="14" t="s">
+      <c r="B78" s="22" t="s">
         <v>257</v>
       </c>
-      <c r="C78" s="14" t="s">
+      <c r="C78" s="22" t="s">
         <v>126</v>
       </c>
-      <c r="D78" s="14" t="s">
+      <c r="D78" s="22" t="s">
         <v>280</v>
       </c>
-      <c r="E78" s="14" t="s">
+      <c r="E78" s="22" t="s">
         <v>281</v>
       </c>
-      <c r="F78" s="14" t="s">
+      <c r="F78" s="22" t="s">
         <v>282</v>
       </c>
-      <c r="G78" s="15" t="s">
+      <c r="G78" s="23" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="79" ht="25.5" spans="1:7">
-      <c r="A79" s="13" t="s">
+      <c r="A79" s="21" t="s">
         <v>256</v>
       </c>
-      <c r="B79" s="14" t="s">
+      <c r="B79" s="22" t="s">
         <v>257</v>
       </c>
-      <c r="C79" s="14" t="s">
+      <c r="C79" s="22" t="s">
         <v>130</v>
       </c>
-      <c r="D79" s="14" t="s">
+      <c r="D79" s="22" t="s">
         <v>283</v>
       </c>
-      <c r="E79" s="14" t="s">
+      <c r="E79" s="22" t="s">
         <v>284</v>
       </c>
-      <c r="F79" s="14" t="s">
+      <c r="F79" s="22" t="s">
         <v>285</v>
       </c>
-      <c r="G79" s="15" t="s">
+      <c r="G79" s="23" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="80" ht="25.5" spans="1:7">
-      <c r="A80" s="13" t="s">
+      <c r="A80" s="21" t="s">
         <v>256</v>
       </c>
-      <c r="B80" s="14" t="s">
+      <c r="B80" s="22" t="s">
         <v>257</v>
       </c>
-      <c r="C80" s="16" t="s">
+      <c r="C80" s="24" t="s">
         <v>134</v>
       </c>
-      <c r="D80" s="14" t="s">
+      <c r="D80" s="22" t="s">
         <v>286</v>
       </c>
-      <c r="E80" s="16" t="s">
+      <c r="E80" s="24" t="s">
         <v>287</v>
       </c>
-      <c r="F80" s="14" t="s">
+      <c r="F80" s="22" t="s">
         <v>288</v>
       </c>
-      <c r="G80" s="15" t="s">
+      <c r="G80" s="23" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="81" ht="25.5" spans="1:7">
-      <c r="A81" s="13" t="s">
+      <c r="A81" s="21" t="s">
         <v>289</v>
       </c>
-      <c r="B81" s="14" t="s">
+      <c r="B81" s="22" t="s">
         <v>290</v>
       </c>
-      <c r="C81" s="14" t="s">
+      <c r="C81" s="22" t="s">
         <v>291</v>
       </c>
-      <c r="D81" s="14" t="s">
+      <c r="D81" s="22" t="s">
         <v>292</v>
       </c>
-      <c r="E81" s="14" t="s">
+      <c r="E81" s="22" t="s">
         <v>293</v>
       </c>
-      <c r="F81" s="14" t="s">
+      <c r="F81" s="22" t="s">
         <v>294</v>
       </c>
-      <c r="G81" s="15" t="s">
+      <c r="G81" s="23" t="s">
         <v>295</v>
       </c>
     </row>
     <row r="82" ht="25.5" spans="1:7">
-      <c r="A82" s="13" t="s">
+      <c r="A82" s="21" t="s">
         <v>289</v>
       </c>
-      <c r="B82" s="14" t="s">
+      <c r="B82" s="22" t="s">
         <v>290</v>
       </c>
-      <c r="C82" s="14" t="s">
+      <c r="C82" s="22" t="s">
         <v>296</v>
       </c>
-      <c r="D82" s="14" t="s">
+      <c r="D82" s="22" t="s">
         <v>297</v>
       </c>
-      <c r="E82" s="14" t="s">
+      <c r="E82" s="22" t="s">
         <v>298</v>
       </c>
-      <c r="F82" s="14" t="s">
+      <c r="F82" s="22" t="s">
         <v>299</v>
       </c>
-      <c r="G82" s="15" t="s">
+      <c r="G82" s="23" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="83" ht="25.5" spans="1:7">
-      <c r="A83" s="13" t="s">
+      <c r="A83" s="21" t="s">
         <v>289</v>
       </c>
-      <c r="B83" s="14" t="s">
+      <c r="B83" s="22" t="s">
         <v>290</v>
       </c>
-      <c r="C83" s="14" t="s">
+      <c r="C83" s="22" t="s">
         <v>300</v>
       </c>
-      <c r="D83" s="14" t="s">
+      <c r="D83" s="22" t="s">
         <v>301</v>
       </c>
-      <c r="E83" s="14" t="s">
+      <c r="E83" s="22" t="s">
         <v>302</v>
       </c>
-      <c r="F83" s="14" t="s">
+      <c r="F83" s="22" t="s">
         <v>303</v>
       </c>
-      <c r="G83" s="15" t="s">
+      <c r="G83" s="23" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="84" ht="25.5" spans="1:7">
-      <c r="A84" s="13" t="s">
+      <c r="A84" s="21" t="s">
         <v>289</v>
       </c>
-      <c r="B84" s="14" t="s">
+      <c r="B84" s="22" t="s">
         <v>290</v>
       </c>
-      <c r="C84" s="14" t="s">
+      <c r="C84" s="22" t="s">
         <v>304</v>
       </c>
-      <c r="D84" s="14" t="s">
+      <c r="D84" s="22" t="s">
         <v>305</v>
       </c>
-      <c r="E84" s="14" t="s">
+      <c r="E84" s="22" t="s">
         <v>306</v>
       </c>
-      <c r="F84" s="14" t="s">
+      <c r="F84" s="22" t="s">
         <v>307</v>
       </c>
-      <c r="G84" s="15" t="s">
+      <c r="G84" s="23" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="85" ht="25.5" spans="1:7">
-      <c r="A85" s="13" t="s">
+      <c r="A85" s="21" t="s">
         <v>289</v>
       </c>
-      <c r="B85" s="14" t="s">
+      <c r="B85" s="22" t="s">
         <v>290</v>
       </c>
-      <c r="C85" s="14" t="s">
+      <c r="C85" s="22" t="s">
         <v>308</v>
       </c>
-      <c r="D85" s="14" t="s">
+      <c r="D85" s="22" t="s">
         <v>309</v>
       </c>
-      <c r="E85" s="14" t="s">
+      <c r="E85" s="22" t="s">
         <v>310</v>
       </c>
-      <c r="F85" s="14" t="s">
+      <c r="F85" s="22" t="s">
         <v>311</v>
       </c>
-      <c r="G85" s="15" t="s">
+      <c r="G85" s="23" t="s">
         <v>14</v>
       </c>
     </row>
@@ -4556,66 +4878,66 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1" spans="1:4">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="9" t="s">
         <v>312</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:4">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="10" t="s">
         <v>313</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="10" t="s">
         <v>314</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="10" t="s">
         <v>315</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="10" t="s">
         <v>316</v>
       </c>
     </row>
     <row r="4" ht="26.4" customHeight="1" spans="1:4">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="12" t="s">
         <v>317</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="12" t="s">
         <v>318</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="12" t="s">
         <v>319</v>
       </c>
     </row>
     <row r="5" ht="26.4" customHeight="1" spans="1:4">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="13" t="s">
         <v>215</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="14" t="s">
         <v>320</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="14" t="s">
         <v>321</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="14" t="s">
         <v>322</v>
       </c>
     </row>
     <row r="6" ht="26.4" customHeight="1" spans="1:4">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="15" t="s">
         <v>218</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="16" t="s">
         <v>323</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="16" t="s">
         <v>324</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="16" t="s">
         <v>325</v>
       </c>
     </row>
@@ -4626,4 +4948,710 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E60"/>
+  <sheetFormatPr defaultColWidth="8.96666666666667" defaultRowHeight="13.5" outlineLevelCol="4"/>
+  <cols>
+    <col min="1" max="1" width="12.3166666666667" customWidth="1"/>
+    <col min="2" max="2" width="12.5916666666667" customWidth="1"/>
+    <col min="3" max="3" width="13.8166666666667" customWidth="1"/>
+    <col min="4" max="4" width="16.6583333333333" customWidth="1"/>
+    <col min="5" max="5" width="42.9" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="4"/>
+      <c r="B5" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="5"/>
+      <c r="B6" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="5"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="4"/>
+      <c r="B10" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="4"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="4"/>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="4"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="4"/>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="4"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="4"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="4"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="4"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="4"/>
+      <c r="B19" s="4"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="4"/>
+      <c r="B20" s="4"/>
+      <c r="C20" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="4"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="4"/>
+      <c r="B22" s="4"/>
+      <c r="C22" s="4"/>
+      <c r="D22" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5"/>
+      <c r="B23" s="5"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5"/>
+      <c r="B25" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="26" ht="17" customHeight="1" spans="1:5">
+      <c r="A26" s="6" t="s">
+        <v>348</v>
+      </c>
+      <c r="B26" s="2"/>
+      <c r="C26" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="7"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="4"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="7"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="4"/>
+      <c r="D28" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="7"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="5"/>
+      <c r="D29" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="7"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="7"/>
+      <c r="B31" s="2"/>
+      <c r="C31" s="4"/>
+      <c r="D31" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="7"/>
+      <c r="B32" s="2"/>
+      <c r="C32" s="5"/>
+      <c r="D32" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="7"/>
+      <c r="B33" s="2"/>
+      <c r="C33" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="7"/>
+      <c r="B34" s="2"/>
+      <c r="C34" s="4"/>
+      <c r="D34" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="7"/>
+      <c r="B35" s="2"/>
+      <c r="C35" s="4"/>
+      <c r="D35" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="7"/>
+      <c r="B36" s="2"/>
+      <c r="C36" s="4"/>
+      <c r="D36" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="7"/>
+      <c r="B37" s="2"/>
+      <c r="C37" s="4"/>
+      <c r="D37" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="7"/>
+      <c r="B38" s="2"/>
+      <c r="C38" s="4"/>
+      <c r="D38" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="7"/>
+      <c r="B39" s="2"/>
+      <c r="C39" s="4"/>
+      <c r="D39" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="7"/>
+      <c r="B40" s="2"/>
+      <c r="C40" s="5"/>
+      <c r="D40" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="7"/>
+      <c r="B41" s="2"/>
+      <c r="C41" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="D41" s="2"/>
+      <c r="E41" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="7"/>
+      <c r="B42" s="2"/>
+      <c r="C42" s="4"/>
+      <c r="D42" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="7"/>
+      <c r="B43" s="2"/>
+      <c r="C43" s="5"/>
+      <c r="D43" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="7"/>
+      <c r="B44" s="2"/>
+      <c r="C44" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="D44" s="2"/>
+      <c r="E44" s="2" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="7"/>
+      <c r="B45" s="2"/>
+      <c r="C45" s="4"/>
+      <c r="D45" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="7"/>
+      <c r="B46" s="2"/>
+      <c r="C46" s="5"/>
+      <c r="D46" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="7"/>
+      <c r="B47" s="2"/>
+      <c r="C47" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="D47" s="2"/>
+      <c r="E47" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="7"/>
+      <c r="B48" s="2"/>
+      <c r="C48" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="D48" s="2"/>
+      <c r="E48" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="7"/>
+      <c r="B49" s="2"/>
+      <c r="C49" s="4"/>
+      <c r="D49" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="7"/>
+      <c r="B50" s="2"/>
+      <c r="C50" s="4"/>
+      <c r="D50" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="7"/>
+      <c r="B51" s="2"/>
+      <c r="C51" s="5"/>
+      <c r="D51" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="7"/>
+      <c r="B52" s="2"/>
+      <c r="C52" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="D52" s="2"/>
+      <c r="E52" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="7"/>
+      <c r="B53" s="2"/>
+      <c r="C53" s="4"/>
+      <c r="D53" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="7"/>
+      <c r="B54" s="2"/>
+      <c r="C54" s="4"/>
+      <c r="D54" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="7"/>
+      <c r="B55" s="2"/>
+      <c r="C55" s="4"/>
+      <c r="D55" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="7"/>
+      <c r="B56" s="2"/>
+      <c r="C56" s="4"/>
+      <c r="D56" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="7"/>
+      <c r="B57" s="2"/>
+      <c r="C57" s="4"/>
+      <c r="D57" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="7"/>
+      <c r="B58" s="2"/>
+      <c r="C58" s="5"/>
+      <c r="D58" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="7"/>
+      <c r="B59" s="2"/>
+      <c r="C59" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="D59" s="2"/>
+      <c r="E59" s="2" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="8"/>
+      <c r="B60" s="2"/>
+      <c r="C60" s="5"/>
+      <c r="D60" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>376</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="19">
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="A9:A23"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="A26:A60"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="B10:B23"/>
+    <mergeCell ref="C11:C17"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="C20:C23"/>
+    <mergeCell ref="C26:C29"/>
+    <mergeCell ref="C30:C32"/>
+    <mergeCell ref="C33:C40"/>
+    <mergeCell ref="C41:C43"/>
+    <mergeCell ref="C44:C46"/>
+    <mergeCell ref="C48:C51"/>
+    <mergeCell ref="C52:C58"/>
+    <mergeCell ref="C59:C60"/>
+    <mergeCell ref="D18:D19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>